--- a/edb_data/Nand Flash.xlsx
+++ b/edb_data/Nand Flash.xlsx
@@ -696,19 +696,13 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -33226,13 +33220,13 @@
       </c>
     </row>
     <row r="2906" spans="1:3">
-      <c r="A2906" s="5">
+      <c r="A2906" s="3">
         <v>41429</v>
       </c>
-      <c r="B2906" s="6">
+      <c r="B2906" s="4">
         <v>6.158</v>
       </c>
-      <c r="C2906" s="6">
+      <c r="C2906" s="4">
         <v>3.946</v>
       </c>
     </row>

--- a/edb_data/Nand Flash.xlsx
+++ b/edb_data/Nand Flash.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="27948" windowHeight="11855"/>
+    <workbookView windowWidth="22188" windowHeight="8460"/>
   </bookViews>
   <sheets>
     <sheet name="现货平均价_NAND Flash(64G" sheetId="1" r:id="rId1"/>
@@ -12,7 +12,7 @@
   <externalReferences>
     <externalReference r:id="rId2"/>
   </externalReferences>
-  <calcPr calcId="191029" calcMode="manual"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>

--- a/edb_data/Nand Flash.xlsx
+++ b/edb_data/Nand Flash.xlsx
@@ -696,19 +696,13 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -33248,13 +33242,13 @@
       </c>
     </row>
     <row r="2908" spans="1:3">
-      <c r="A2908" s="5">
+      <c r="A2908" s="3">
         <v>41429</v>
       </c>
-      <c r="B2908" s="6">
+      <c r="B2908" s="4">
         <v>6.158</v>
       </c>
-      <c r="C2908" s="6">
+      <c r="C2908" s="4">
         <v>3.946</v>
       </c>
     </row>
